--- a/Synsam modell.xlsx
+++ b/Synsam modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E70CF8-82CE-F841-B986-255DA753417B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD223B00-AA85-9445-853C-8ED38445C7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17240" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
+    <workbookView xWindow="25080" yWindow="500" windowWidth="26120" windowHeight="26740" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="221">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -726,9 +726,6 @@
     <t>08.06.26: Synsam kjøper tilbake 125 000 aksjer</t>
   </si>
   <si>
-    <t>21.08.25: Synsam starter tilbakekjøpsprgram for å justerer kapitalstrukturen sin</t>
-  </si>
-  <si>
     <t>P/B</t>
   </si>
   <si>
@@ -760,19 +757,56 @@
   </si>
   <si>
     <t>14.09.26: Synsam inngår samarbeid med Carola og blir en ambasadør for Synsam. Hennes egen kolleksjon vil bli tilgjengligjort for salg tidlig 2027</t>
+  </si>
+  <si>
+    <t>20.07.26: Synsam kjøper tilbake 100 000 aksjer</t>
+  </si>
+  <si>
+    <t>27.07.26: Synsam kjøper tilbake 50 000 aksjer</t>
+  </si>
+  <si>
+    <t>03.08.26: Synsam kjøper tilbake 122 000 aksjer</t>
+  </si>
+  <si>
+    <t>10.08.26: Synsam kjøper tilbake 104 000 aksjer</t>
+  </si>
+  <si>
+    <t>17.08.26: Synsam kjøper tilbake  100 000 aksjer</t>
+  </si>
+  <si>
+    <t>24.08.26: Synsam kjøper tilbale 95 000 aksjer</t>
+  </si>
+  <si>
+    <t>31.08.26: Synsam kjøper tilbake 100 000 aksjer</t>
+  </si>
+  <si>
+    <t>07.09.26: Synsam kjøper tilbake 100 000 aksjer</t>
+  </si>
+  <si>
+    <t>14.09.26: Synsam kjøper tilbake 100 000 aksjer</t>
+  </si>
+  <si>
+    <t>21.09.26: Synsam kjøper tilbake 100 000 aksjer</t>
+  </si>
+  <si>
+    <t>28.09.26: Synsam kjøper tilbake 100 000 akskjer</t>
+  </si>
+  <si>
+    <t>21.08.25: Synsam starter tilbakekjøpsprgram for å justerer kapitalstrukturen sin 160 SEKm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="8" formatCode="&quot;kr&quot;\ #,##0.00_);[Red]\(&quot;kr&quot;\ #,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
     <numFmt numFmtId="167" formatCode="#,##0.0000"/>
     <numFmt numFmtId="168" formatCode="0.00%"/>
+    <numFmt numFmtId="169" formatCode="0.0\ %"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -980,7 +1014,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1066,6 +1100,12 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2187,50 +2227,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6FABC2-1253-924E-8CB2-F0C03750A097}">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="10.83203125" style="2"/>
     <col min="7" max="7" width="18.83203125" style="2" customWidth="1"/>
     <col min="8" max="13" width="10.83203125" style="2"/>
-    <col min="14" max="14" width="21" style="2" customWidth="1"/>
-    <col min="15" max="15" width="15" style="2" customWidth="1"/>
+    <col min="14" max="14" width="21" style="82" customWidth="1"/>
+    <col min="15" max="15" width="15" style="15" customWidth="1"/>
     <col min="16" max="16" width="26.5" style="2" customWidth="1"/>
-    <col min="17" max="17" width="10.1640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="17" style="2" customWidth="1"/>
+    <col min="17" max="17" width="11.6640625" style="15" customWidth="1"/>
+    <col min="18" max="18" width="17" style="15" customWidth="1"/>
     <col min="19" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="I1" s="1"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G3" s="2" t="s">
         <v>152</v>
       </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G4" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="G5" s="2" t="s">
         <v>155</v>
       </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="G6" s="2" t="s">
         <v>154</v>
       </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="G7" s="2" t="s">
         <v>156</v>
       </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
@@ -2266,11 +2336,39 @@
       <c r="G10" s="2" t="s">
         <v>158</v>
       </c>
+      <c r="N10" s="82">
+        <v>45901</v>
+      </c>
+      <c r="O10" s="15">
+        <v>100000</v>
+      </c>
+      <c r="P10" s="15">
+        <f>O10</f>
+        <v>100000</v>
+      </c>
+      <c r="Q10" s="15">
+        <f>1147566+1117700+1136668+1149502+1167842</f>
+        <v>5719278</v>
+      </c>
+      <c r="R10" s="15">
+        <f>Q10</f>
+        <v>5719278</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G11" s="2" t="s">
         <v>159</v>
       </c>
+      <c r="N11" s="82">
+        <v>45908</v>
+      </c>
+      <c r="O11" s="15">
+        <v>100000</v>
+      </c>
+      <c r="P11" s="15">
+        <f>SUM(O10:O11)</f>
+        <v>200000</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G12" s="2" t="s">
@@ -2284,7 +2382,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G17" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2297,207 +2395,262 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>124</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>130</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>198</v>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -2674,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <v>55.8</v>
+        <v>53</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>49</v>
@@ -2921,7 +3074,7 @@
       </c>
       <c r="B6" s="8">
         <f>B4*B5</f>
-        <v>7969.2522119999994</v>
+        <v>7569.3614200000002</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>51</v>
@@ -3317,7 +3470,7 @@
       </c>
       <c r="B9" s="9">
         <f>B6-B7+B8</f>
-        <v>10974.252211999999</v>
+        <v>10574.361420000001</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>54</v>
@@ -3850,7 +4003,7 @@
     </row>
     <row r="13" spans="1:41" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B13" s="10">
         <f>(B8-B7)/AF9</f>
@@ -4122,11 +4275,11 @@
     </row>
     <row r="15" spans="1:41" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B15" s="11">
         <f>B6/+T55</f>
-        <v>3.0580399892555636</v>
+        <v>2.9045899539524176</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>60</v>
@@ -5891,603 +6044,607 @@
         <v>96.518484830478826</v>
       </c>
     </row>
-    <row r="26" spans="1:205" x14ac:dyDescent="0.25">
-      <c r="C26" s="13" t="s">
+    <row r="26" spans="1:205" s="79" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="80"/>
+      <c r="C26" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="79">
         <f t="shared" ref="D26:S26" si="42">D6/D4</f>
         <v>0.79568106312292364</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="79">
         <f t="shared" si="42"/>
         <v>0.73992932862190808</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="79">
         <f t="shared" si="42"/>
         <v>0.7415730337078652</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="79">
         <f t="shared" si="42"/>
         <v>0.77132616487455197</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="79">
         <f t="shared" si="42"/>
         <v>0.76771929824561402</v>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="79">
         <f t="shared" si="42"/>
         <v>0.74305555555555558</v>
       </c>
-      <c r="J26" s="13">
+      <c r="J26" s="79">
         <f t="shared" si="42"/>
         <v>0.75388776200135221</v>
       </c>
-      <c r="K26" s="13">
+      <c r="K26" s="79">
         <f t="shared" si="42"/>
         <v>0.76953907815631262</v>
       </c>
-      <c r="L26" s="13">
+      <c r="L26" s="79">
         <f t="shared" si="42"/>
         <v>0.759765625</v>
       </c>
-      <c r="M26" s="13">
+      <c r="M26" s="79">
         <f t="shared" si="42"/>
         <v>0.7459862385321101</v>
       </c>
-      <c r="N26" s="13">
+      <c r="N26" s="79">
         <f t="shared" si="42"/>
         <v>0.74289324068224893</v>
       </c>
-      <c r="O26" s="13">
+      <c r="O26" s="79">
         <f t="shared" si="42"/>
         <v>0.77637130801687759</v>
       </c>
-      <c r="P26" s="13">
+      <c r="P26" s="79">
         <f t="shared" si="42"/>
         <v>0.74524495677233427</v>
       </c>
-      <c r="Q26" s="13">
+      <c r="Q26" s="79">
         <f t="shared" si="42"/>
         <v>0.73628129994672353</v>
       </c>
-      <c r="R26" s="13">
+      <c r="R26" s="79">
         <f t="shared" si="42"/>
         <v>0.7347404449515117</v>
       </c>
-      <c r="S26" s="13">
+      <c r="S26" s="79">
         <f t="shared" si="42"/>
         <v>0.7715376226826608</v>
       </c>
-      <c r="T26" s="13">
+      <c r="T26" s="79">
         <f t="shared" ref="T26:U26" si="43">T6/T4</f>
         <v>0.76179900055524707</v>
       </c>
-      <c r="U26" s="13">
+      <c r="U26" s="79">
         <f t="shared" si="43"/>
         <v>0.7400288322921672</v>
       </c>
-      <c r="V26" s="13"/>
-      <c r="W26" s="13"/>
-      <c r="X26" s="13"/>
-      <c r="Y26" s="13"/>
-      <c r="Z26" s="13">
+      <c r="Z26" s="79">
         <f t="shared" ref="Z26:AO26" si="44">Z6/Z4</f>
         <v>0.75310880829015547</v>
       </c>
-      <c r="AA26" s="13">
+      <c r="AA26" s="79">
         <f t="shared" si="44"/>
         <v>0.76988155668358715</v>
       </c>
-      <c r="AB26" s="13">
+      <c r="AB26" s="79">
         <f t="shared" si="44"/>
         <v>0.76088988595999252</v>
       </c>
-      <c r="AC26" s="13">
+      <c r="AC26" s="79">
         <f t="shared" si="44"/>
         <v>0.7582289055973267</v>
       </c>
-      <c r="AD26" s="13">
+      <c r="AD26" s="79">
         <f t="shared" si="44"/>
         <v>0.75605642440969023</v>
       </c>
-      <c r="AE26" s="13">
+      <c r="AE26" s="79">
         <f t="shared" si="44"/>
         <v>0.74708333333333332</v>
       </c>
-      <c r="AF26" s="26">
+      <c r="AF26" s="80">
         <f t="shared" si="44"/>
         <v>0.75</v>
       </c>
-      <c r="AG26" s="13">
+      <c r="AG26" s="79">
         <f t="shared" si="44"/>
         <v>0.75</v>
       </c>
-      <c r="AH26" s="13">
+      <c r="AH26" s="79">
         <f t="shared" si="44"/>
         <v>0.75</v>
       </c>
-      <c r="AI26" s="13">
+      <c r="AI26" s="79">
         <f t="shared" si="44"/>
         <v>0.75</v>
       </c>
-      <c r="AJ26" s="13">
+      <c r="AJ26" s="79">
         <f t="shared" si="44"/>
         <v>0.75</v>
       </c>
-      <c r="AK26" s="13">
+      <c r="AK26" s="79">
         <f t="shared" si="44"/>
         <v>0.75</v>
       </c>
-      <c r="AL26" s="13">
+      <c r="AL26" s="79">
         <f t="shared" si="44"/>
         <v>0.75000000000000011</v>
       </c>
-      <c r="AM26" s="13">
+      <c r="AM26" s="79">
         <f t="shared" si="44"/>
         <v>0.75</v>
       </c>
-      <c r="AN26" s="13">
+      <c r="AN26" s="79">
         <f t="shared" si="44"/>
         <v>0.74999999999999989</v>
       </c>
-      <c r="AO26" s="13">
+      <c r="AO26" s="79">
         <f t="shared" si="44"/>
         <v>0.75</v>
       </c>
-      <c r="AQ26" s="1" t="s">
+      <c r="AQ26" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="AR26" s="14">
+      <c r="AR26" s="81">
         <f>(AR25-B4)/B4</f>
-        <v>0.72972195036700416</v>
-      </c>
-    </row>
-    <row r="27" spans="1:205" x14ac:dyDescent="0.25">
-      <c r="C27" s="2" t="s">
+        <v>0.82110348736752503</v>
+      </c>
+    </row>
+    <row r="27" spans="1:205" s="79" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="80"/>
+      <c r="C27" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="79">
         <f t="shared" ref="D27:S27" si="45">D9/D4</f>
         <v>0.24335548172757476</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="79">
         <f t="shared" si="45"/>
         <v>0.24593639575971732</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="79">
         <f t="shared" si="45"/>
         <v>0.22621722846441947</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="79">
         <f t="shared" si="45"/>
         <v>0.19569892473118281</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="79">
         <f t="shared" si="45"/>
         <v>0.22315789473684211</v>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="79">
         <f t="shared" si="45"/>
         <v>0.25315656565656564</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="79">
         <f t="shared" si="45"/>
         <v>0.25287356321839083</v>
       </c>
-      <c r="K27" s="13">
+      <c r="K27" s="79">
         <f t="shared" si="45"/>
         <v>0.23246492985971945</v>
       </c>
-      <c r="L27" s="13">
+      <c r="L27" s="79">
         <f t="shared" si="45"/>
         <v>0.23372395833333334</v>
       </c>
-      <c r="M27" s="13">
+      <c r="M27" s="79">
         <f t="shared" si="45"/>
         <v>0.26892201834862384</v>
       </c>
-      <c r="N27" s="13">
+      <c r="N27" s="79">
         <f t="shared" si="45"/>
         <v>0.2406822488945041</v>
       </c>
-      <c r="O27" s="13">
+      <c r="O27" s="79">
         <f t="shared" si="45"/>
         <v>0.23327305605786619</v>
       </c>
-      <c r="P27" s="13">
+      <c r="P27" s="79">
         <f t="shared" si="45"/>
         <v>0.21613832853025935</v>
       </c>
-      <c r="Q27" s="13">
+      <c r="Q27" s="79">
         <f t="shared" si="45"/>
         <v>0.25039957378795952</v>
       </c>
-      <c r="R27" s="13">
+      <c r="R27" s="79">
         <f t="shared" si="45"/>
         <v>0.23844837421563034</v>
       </c>
-      <c r="S27" s="13">
+      <c r="S27" s="79">
         <f t="shared" si="45"/>
         <v>0.23227917121046893</v>
       </c>
-      <c r="T27" s="13">
+      <c r="T27" s="79">
         <f t="shared" ref="T27" si="46">T9/T4</f>
         <v>0.2220988339811216</v>
       </c>
-      <c r="U27" s="13">
+      <c r="U27" s="79">
         <f>U9/U4</f>
         <v>0.24651609802979338</v>
       </c>
-      <c r="Z27" s="13">
+      <c r="Z27" s="79">
         <f t="shared" ref="Z27:AO27" si="47">Z9/Z4</f>
         <v>0.24196891191709843</v>
       </c>
-      <c r="AA27" s="13">
+      <c r="AA27" s="79">
         <f t="shared" si="47"/>
         <v>0.2512690355329949</v>
       </c>
-      <c r="AB27" s="13">
+      <c r="AB27" s="79">
         <f t="shared" si="47"/>
         <v>0.22751916246027296</v>
       </c>
-      <c r="AC27" s="13">
+      <c r="AC27" s="79">
         <f t="shared" si="47"/>
         <v>0.24076858813700919</v>
       </c>
-      <c r="AD27" s="13">
+      <c r="AD27" s="79">
         <f t="shared" si="47"/>
         <v>0.24471021159153633</v>
       </c>
-      <c r="AE27" s="13">
+      <c r="AE27" s="79">
         <f t="shared" si="47"/>
         <v>0.23444444444444446</v>
       </c>
-      <c r="AF27" s="26">
+      <c r="AF27" s="80">
         <f t="shared" si="47"/>
         <v>0.23879439784612194</v>
       </c>
-      <c r="AG27" s="13">
+      <c r="AG27" s="79">
         <f t="shared" si="47"/>
         <v>0.24120574502609313</v>
       </c>
-      <c r="AH27" s="13">
+      <c r="AH27" s="79">
         <f t="shared" si="47"/>
         <v>0.24360571792691349</v>
       </c>
-      <c r="AI27" s="13">
+      <c r="AI27" s="79">
         <f t="shared" si="47"/>
         <v>0.24360571792691346</v>
       </c>
-      <c r="AJ27" s="13">
+      <c r="AJ27" s="79">
         <f t="shared" si="47"/>
         <v>0.24360571792691352</v>
       </c>
-      <c r="AK27" s="13">
+      <c r="AK27" s="79">
         <f t="shared" si="47"/>
         <v>0.24360571792691363</v>
       </c>
-      <c r="AL27" s="13">
+      <c r="AL27" s="79">
         <f t="shared" si="47"/>
         <v>0.24360571792691366</v>
       </c>
-      <c r="AM27" s="13">
+      <c r="AM27" s="79">
         <f t="shared" si="47"/>
         <v>0.24360571792691355</v>
       </c>
-      <c r="AN27" s="13">
+      <c r="AN27" s="79">
         <f t="shared" si="47"/>
         <v>0.24360571792691357</v>
       </c>
-      <c r="AO27" s="13">
+      <c r="AO27" s="79">
         <f t="shared" si="47"/>
         <v>0.24360571792691363</v>
       </c>
     </row>
-    <row r="28" spans="1:205" x14ac:dyDescent="0.25">
-      <c r="C28" s="2" t="s">
+    <row r="28" spans="1:205" s="79" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="80"/>
+      <c r="C28" s="79" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="79">
         <f t="shared" ref="D28:S28" si="48">D11/D4</f>
         <v>0.14700996677740863</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="79">
         <f t="shared" si="48"/>
         <v>0.15901060070671377</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="79">
         <f t="shared" si="48"/>
         <v>0.12584269662921349</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="79">
         <f t="shared" si="48"/>
         <v>9.1039426523297495E-2</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="79">
         <f t="shared" si="48"/>
         <v>0.12</v>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="79">
         <f t="shared" si="48"/>
         <v>0.16224747474747475</v>
       </c>
-      <c r="J28" s="13">
+      <c r="J28" s="79">
         <f t="shared" si="48"/>
         <v>0.15077755240027046</v>
       </c>
-      <c r="K28" s="13">
+      <c r="K28" s="79">
         <f t="shared" si="48"/>
         <v>0.13360053440213762</v>
       </c>
-      <c r="L28" s="13">
+      <c r="L28" s="79">
         <f t="shared" si="48"/>
         <v>0.13411458333333334</v>
       </c>
-      <c r="M28" s="13">
+      <c r="M28" s="79">
         <f t="shared" si="48"/>
         <v>0.17889908256880735</v>
       </c>
-      <c r="N28" s="13">
+      <c r="N28" s="79">
         <f t="shared" si="48"/>
         <v>0.13897662665824384</v>
       </c>
-      <c r="O28" s="13">
+      <c r="O28" s="79">
         <f t="shared" si="48"/>
         <v>0.13200723327305605</v>
       </c>
-      <c r="P28" s="13">
+      <c r="P28" s="79">
         <f t="shared" si="48"/>
         <v>0.11930835734870317</v>
       </c>
-      <c r="Q28" s="13">
+      <c r="Q28" s="79">
         <f t="shared" si="48"/>
         <v>0.15929675013319125</v>
       </c>
-      <c r="R28" s="13">
+      <c r="R28" s="79">
         <f t="shared" si="48"/>
         <v>0.13633770678836279</v>
       </c>
-      <c r="S28" s="13">
+      <c r="S28" s="79">
         <f t="shared" si="48"/>
         <v>0.13413304252998909</v>
       </c>
-      <c r="T28" s="13">
+      <c r="T28" s="79">
         <f t="shared" ref="T28:U28" si="49">T11/T4</f>
         <v>0.12104386451971128</v>
       </c>
-      <c r="U28" s="13">
+      <c r="U28" s="79">
         <f t="shared" si="49"/>
         <v>0.15665545410860163</v>
       </c>
-      <c r="Z28" s="13">
+      <c r="Z28" s="79">
         <f t="shared" ref="Z28:AO28" si="50">Z11/Z4</f>
         <v>0.12668393782383419</v>
       </c>
-      <c r="AA28" s="13">
+      <c r="AA28" s="79">
         <f t="shared" si="50"/>
         <v>0.15313028764805414</v>
       </c>
-      <c r="AB28" s="13">
+      <c r="AB28" s="79">
         <f t="shared" si="50"/>
         <v>0.12357449990652458</v>
       </c>
-      <c r="AC28" s="13">
+      <c r="AC28" s="79">
         <f t="shared" si="50"/>
         <v>0.1368421052631579</v>
       </c>
-      <c r="AD28" s="13">
+      <c r="AD28" s="79">
         <f t="shared" si="50"/>
         <v>0.14520085863232138</v>
       </c>
-      <c r="AE28" s="13">
+      <c r="AE28" s="79">
         <f t="shared" si="50"/>
         <v>0.13694444444444445</v>
       </c>
-      <c r="AF28" s="26">
+      <c r="AF28" s="80">
         <f t="shared" si="50"/>
         <v>0.14300895723309512</v>
       </c>
-      <c r="AG28" s="13">
+      <c r="AG28" s="79">
         <f t="shared" si="50"/>
         <v>0.14542030441306628</v>
       </c>
-      <c r="AH28" s="13">
+      <c r="AH28" s="79">
         <f t="shared" si="50"/>
         <v>0.15233845847487848</v>
       </c>
-      <c r="AI28" s="13">
+      <c r="AI28" s="79">
         <f t="shared" si="50"/>
         <v>0.15664351788299333</v>
       </c>
-      <c r="AJ28" s="13">
+      <c r="AJ28" s="79">
         <f t="shared" si="50"/>
         <v>0.16074550845110283</v>
       </c>
-      <c r="AK28" s="13">
+      <c r="AK28" s="79">
         <f t="shared" si="50"/>
         <v>0.16465400889807513</v>
       </c>
-      <c r="AL28" s="13">
+      <c r="AL28" s="79">
         <f t="shared" si="50"/>
         <v>0.1683781461164166</v>
       </c>
-      <c r="AM28" s="13">
+      <c r="AM28" s="79">
         <f t="shared" si="50"/>
         <v>0.17192661648483618</v>
       </c>
-      <c r="AN28" s="13">
+      <c r="AN28" s="79">
         <f t="shared" si="50"/>
         <v>0.17530770617550023</v>
       </c>
-      <c r="AO28" s="13">
+      <c r="AO28" s="79">
         <f t="shared" si="50"/>
         <v>0.17852931050339713</v>
       </c>
     </row>
-    <row r="29" spans="1:205" x14ac:dyDescent="0.25">
-      <c r="C29" s="2" t="s">
+    <row r="29" spans="1:205" s="79" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="80"/>
+      <c r="C29" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="79">
         <f t="shared" ref="D29:S29" si="51">D13/D4</f>
         <v>0.11710963455149502</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="79">
         <f t="shared" si="51"/>
         <v>0.13356890459363957</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="79">
         <f t="shared" si="51"/>
         <v>9.8876404494382023E-2</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="79">
         <f t="shared" si="51"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="79">
         <f t="shared" si="51"/>
         <v>9.3333333333333338E-2</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="79">
         <f t="shared" si="51"/>
         <v>0.13825757575757575</v>
       </c>
-      <c r="J29" s="13">
+      <c r="J29" s="79">
         <f t="shared" si="51"/>
         <v>0.12440838404327248</v>
       </c>
-      <c r="K29" s="13">
+      <c r="K29" s="79">
         <f t="shared" si="51"/>
         <v>0.10754843019372078</v>
       </c>
-      <c r="L29" s="13">
+      <c r="L29" s="79">
         <f t="shared" si="51"/>
         <v>0.111328125</v>
       </c>
-      <c r="M29" s="13">
+      <c r="M29" s="79">
         <f t="shared" si="51"/>
         <v>0.15768348623853212</v>
       </c>
-      <c r="N29" s="13">
+      <c r="N29" s="79">
         <f t="shared" si="51"/>
         <v>0.11813013265950727</v>
       </c>
-      <c r="O29" s="13">
+      <c r="O29" s="79">
         <f t="shared" si="51"/>
         <v>0.11211573236889692</v>
       </c>
-      <c r="P29" s="13">
+      <c r="P29" s="79">
         <f t="shared" si="51"/>
         <v>0.10028818443804034</v>
       </c>
-      <c r="Q29" s="13">
+      <c r="Q29" s="79">
         <f t="shared" si="51"/>
         <v>0.14224826851358552</v>
       </c>
-      <c r="R29" s="13">
+      <c r="R29" s="79">
         <f t="shared" si="51"/>
         <v>0.11808328579577866</v>
       </c>
-      <c r="S29" s="13">
+      <c r="S29" s="79">
         <f t="shared" si="51"/>
         <v>0.11668484187568157</v>
       </c>
-      <c r="T29" s="13">
+      <c r="T29" s="79">
         <f t="shared" ref="T29:U29" si="52">T13/T4</f>
         <v>0.10327595780122155</v>
       </c>
-      <c r="U29" s="13">
+      <c r="U29" s="79">
         <f t="shared" si="52"/>
         <v>0.13935607880826525</v>
       </c>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="13">
+      <c r="V29" s="81"/>
+      <c r="W29" s="81"/>
+      <c r="X29" s="81"/>
+      <c r="Y29" s="81"/>
+      <c r="Z29" s="79">
         <f t="shared" ref="Z29:AO29" si="53">Z13/Z4</f>
         <v>0.10414507772020726</v>
       </c>
-      <c r="AA29" s="13">
+      <c r="AA29" s="79">
         <f t="shared" si="53"/>
         <v>0.13388324873096447</v>
       </c>
-      <c r="AB29" s="13">
+      <c r="AB29" s="79">
         <f t="shared" si="53"/>
         <v>0.10319685922602355</v>
       </c>
-      <c r="AC29" s="13">
+      <c r="AC29" s="79">
         <f t="shared" si="53"/>
         <v>0.11629072681704261</v>
       </c>
-      <c r="AD29" s="13">
+      <c r="AD29" s="79">
         <f t="shared" si="53"/>
         <v>0.12557497700091996</v>
       </c>
-      <c r="AE29" s="13">
+      <c r="AE29" s="79">
         <f t="shared" si="53"/>
         <v>0.11972222222222222</v>
       </c>
-      <c r="AF29" s="26">
+      <c r="AF29" s="80">
         <f t="shared" si="53"/>
         <v>0.12644066480273372</v>
       </c>
-      <c r="AG29" s="13">
+      <c r="AG29" s="79">
         <f t="shared" si="53"/>
         <v>0.12916462127384379</v>
       </c>
-      <c r="AH29" s="13">
+      <c r="AH29" s="79">
         <f t="shared" si="53"/>
         <v>0.13684955284222308</v>
       </c>
-      <c r="AI29" s="13">
+      <c r="AI29" s="79">
         <f t="shared" si="53"/>
         <v>0.14188522100659523</v>
       </c>
-      <c r="AJ29" s="13">
+      <c r="AJ29" s="79">
         <f t="shared" si="53"/>
         <v>0.14668335765378013</v>
       </c>
-      <c r="AK29" s="13">
+      <c r="AK29" s="79">
         <f t="shared" si="53"/>
         <v>0.15125516710062614</v>
       </c>
-      <c r="AL29" s="13">
+      <c r="AL29" s="79">
         <f t="shared" si="53"/>
         <v>0.15561132515846993</v>
       </c>
-      <c r="AM29" s="13">
+      <c r="AM29" s="79">
         <f t="shared" si="53"/>
         <v>0.15976200406264171</v>
       </c>
-      <c r="AN29" s="13">
+      <c r="AN29" s="79">
         <f t="shared" si="53"/>
         <v>0.16371689622605079</v>
       </c>
-      <c r="AO29" s="13">
+      <c r="AO29" s="79">
         <f t="shared" si="53"/>
         <v>0.16748523687231795</v>
       </c>
     </row>
-    <row r="30" spans="1:205" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="26"/>
-      <c r="C30" s="13" t="s">
+    <row r="30" spans="1:205" s="79" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="80"/>
+      <c r="C30" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="AB30" s="13">
+      <c r="AA30" s="79">
+        <f>AA18/AA55</f>
+        <v>2.0572811617587738E-2</v>
+      </c>
+      <c r="AB30" s="79">
         <v>0.129</v>
       </c>
-      <c r="AC30" s="13">
+      <c r="AC30" s="79">
         <v>0.122</v>
       </c>
-      <c r="AD30" s="13">
+      <c r="AD30" s="79">
         <v>0.14499999999999999</v>
       </c>
-      <c r="AE30" s="13">
+      <c r="AE30" s="79">
         <v>0.184</v>
       </c>
-      <c r="AF30" s="26"/>
+      <c r="AF30" s="80"/>
     </row>
     <row r="31" spans="1:205" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="26"/>
@@ -6930,7 +7087,7 @@
     <row r="38" spans="2:41" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="77"/>
       <c r="C38" s="78" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="U38" s="34">
         <v>0.54</v>
@@ -11149,7 +11306,7 @@
         <v>233</v>
       </c>
       <c r="V93" s="15"/>
-      <c r="W93" s="15"/>
+      <c r="W93" s="40"/>
       <c r="X93" s="15"/>
       <c r="Y93" s="15"/>
       <c r="Z93" s="15">
@@ -11169,7 +11326,7 @@
         <v>473</v>
       </c>
       <c r="AD93" s="15">
-        <f t="shared" si="85"/>
+        <f>AD76+AD78+AD84</f>
         <v>155</v>
       </c>
       <c r="AE93" s="15">
@@ -12742,7 +12899,7 @@
     <row r="21" spans="1:29" s="74" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34"/>
       <c r="B21" s="74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G21" s="75"/>
       <c r="H21" s="76"/>
@@ -15125,7 +15282,7 @@
     <row r="54" spans="1:29" s="74" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
       <c r="B54" s="74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G54" s="75"/>
       <c r="H54" s="76"/>
@@ -16645,15 +16802,15 @@
       </c>
       <c r="D5" s="39">
         <f>Modell!$B$9/Modell!AF9</f>
-        <v>5.9486522942493361</v>
+        <v>5.7318893448176818</v>
       </c>
       <c r="E5" s="39">
         <f>Modell!$B$9/Modell!AG9</f>
-        <v>5.5558332906597698</v>
+        <v>5.3533842734599917</v>
       </c>
       <c r="F5" s="39">
         <f>Modell!$B$9/Modell!AH9</f>
-        <v>5.1897150185833238</v>
+        <v>5.0006069856217454</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -16662,15 +16819,15 @@
       </c>
       <c r="D6" s="39">
         <f>Modell!$B$9/Modell!AF13</f>
-        <v>11.234556895263255</v>
+        <v>10.825180860538689</v>
       </c>
       <c r="E6" s="39">
         <f>Modell!$B$9/Modell!AG13</f>
-        <v>10.375123581814227</v>
+        <v>9.9970644388237968</v>
       </c>
       <c r="F6" s="39">
         <f>Modell!$B$9/Modell!AH13</f>
-        <v>9.2382052164660795</v>
+        <v>8.9015742434115737</v>
       </c>
     </row>
     <row r="7" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -16679,15 +16836,15 @@
       </c>
       <c r="D7" s="39">
         <f>Modell!$B$4/Modell!AF20</f>
-        <v>14.157886095740583</v>
+        <v>13.447454535380841</v>
       </c>
       <c r="E7" s="39">
         <f>Modell!$B$4/Modell!AG20</f>
-        <v>12.780617784640711</v>
+        <v>12.139296462113936</v>
       </c>
       <c r="F7" s="39">
         <f>Modell!$B$4/Modell!AH20</f>
-        <v>11.011002412454996</v>
+        <v>10.458478993908868</v>
       </c>
     </row>
   </sheetData>
@@ -16898,7 +17055,7 @@
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <f>V26</f>
-        <v>-0.35745356936161843</v>
+        <v>-0.32350772019581719</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>51</v>
@@ -18850,7 +19007,7 @@
       </c>
       <c r="V26" s="14">
         <f>(V25-Modell!B4)/Modell!B4</f>
-        <v>-0.35745356936161843</v>
+        <v>-0.32350772019581719</v>
       </c>
     </row>
     <row r="27" spans="3:201" x14ac:dyDescent="0.25">
